--- a/config/trainer/skills.xlsx
+++ b/config/trainer/skills.xlsx
@@ -1503,7 +1503,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>資産運用家Ⅰ</t>
+          <t>资产管理Ⅰ</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="R5" s="4" t="inlineStr">
         <is>
-          <t>毎日無料回数+%d</t>
+          <t>每日免费次数+%d</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>ストーリーモード</t>
+          <t>故事模式</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="R6" s="4" t="inlineStr">
         <is>
-          <t>金貨獲得+%d</t>
+          <t>金币获得+%d</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>スタミナ回復(夕食)</t>
+          <t>恢复体力（晚餐）</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="R7" s="4" t="inlineStr">
         <is>
-          <t>スタミナ回復量+%d</t>
+          <t>体力回复量+%d</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>資産運用家Ⅱ</t>
+          <t>资产管理Ⅱ</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>タンパク質Ⅰ</t>
+          <t>蛋白质Ⅰ</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>スタミナ回復(昼食)</t>
+          <t>体力恢复（午餐）</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="R9" s="4" t="inlineStr">
         <is>
-          <t>スタミナ回復量+%d</t>
+          <t>体力回复量+%d</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>人生の如くⅠ</t>
+          <t>像人生一样Ⅰ</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>ハードモード</t>
+          <t>硬模式</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="R10" s="4" t="inlineStr">
         <is>
-          <t>金貨獲得+%d</t>
+          <t>金币获得+%d</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>業界良心</t>
+          <t>行业良心</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>金貨ガチャ</t>
+          <t>金币扭蛋</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="R11" s="4" t="inlineStr">
         <is>
-          <t>毎日無料回数+%d</t>
+          <t>每日免费次数+%d</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -2338,7 +2338,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>スタミナ上限</t>
+          <t>体力上限</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2395,7 +2395,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>資産運用家Ⅲ</t>
+          <t>资产管理Ⅲ</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>金運上昇Ⅰ</t>
+          <t>财运上升Ⅰ</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2558,7 +2558,7 @@
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>金貨ダンジョン</t>
+          <t>金币地牢</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="R14" s="4" t="inlineStr">
         <is>
-          <t>金貨獲得+%d</t>
+          <t>金币获得+%d</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>カフェインⅠ</t>
+          <t>咖啡因Ⅰ</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>スタミナ回復(朝食)</t>
+          <t>恢复体力（早餐）</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>スタミナ回復量+%d</t>
+          <t>体力回复量+%d</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>腕相撲Ⅰ</t>
+          <t>摔跤Ⅰ</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2782,7 +2782,7 @@
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>経験値ダンジョン</t>
+          <t>经验值地牢</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>経験値獲得+%d</t>
+          <t>获得经验值+%d</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>交渉術Ⅰ</t>
+          <t>谈判技巧Ⅰ</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2894,7 +2894,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>経験値アイテム購入</t>
+          <t>购买经验值道具</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>価格割引+%d</t>
+          <t>价格优惠+%d</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>夜のグルメⅠ</t>
+          <t>夜间美食Ⅰ</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>スタミナ回復(夜食)</t>
+          <t>恢复体力（夜宵）</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>スタミナ回復量+%d</t>
+          <t>体力回复量+%d</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>資産運用家Ⅳ</t>
+          <t>资产管理Ⅳ</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>毎日無料回数+%d</t>
+          <t>每日免费次数+%d</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>才能開花Ⅰ</t>
+          <t>才华绽放Ⅰ</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>潜能ダンジョン</t>
+          <t>潜能地牢</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>産出増加+%d</t>
+          <t>产量增加+%d</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>功労者Ⅰ</t>
+          <t>功臣Ⅰ</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>ギルド寄付</t>
+          <t>公会捐赠</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>ギルドコイン獲得+%d</t>
+          <t>公会币获得+%d</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -3454,7 +3454,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>スタミナ上限</t>
+          <t>体力上限</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>交渉術Ⅱ</t>
+          <t>谈判技巧Ⅱ</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>経験値アイテム購入</t>
+          <t>购买经验值道具</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>価格割引+%d</t>
+          <t>价格优惠+%d</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>ストーリーモード</t>
+          <t>故事模式</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3703,7 +3703,7 @@
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>金貨獲得+%d</t>
+          <t>金币获得+%d</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>紳士の矜持Ⅰ</t>
+          <t>绅士的矜持Ⅰ</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>ギフトダンジョン</t>
+          <t>礼品地牢</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>産出増加+%d</t>
+          <t>产量增加+%d</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>スタミナ回復(夕食)</t>
+          <t>恢复体力（晚餐）</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3927,7 +3927,7 @@
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>スタミナ回復量+%d</t>
+          <t>体力回复量+%d</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3959,7 +3959,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>これは仕事</t>
+          <t>这是工作</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4014,14 +4014,14 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
+          <t>日常任务</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
           <t>日常任務</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>日常任務</t>
-        </is>
-      </c>
       <c r="O27" t="inlineStr">
         <is>
           <t>Daily Mission</t>
@@ -4039,7 +4039,7 @@
       </c>
       <c r="R27" s="4" t="inlineStr">
         <is>
-          <t>経験値獲得+%d</t>
+          <t>获得经验值+%d</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>人生の如くⅡ</t>
+          <t>像人生一样Ⅱ</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>ハードモード</t>
+          <t>硬模式</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="R28" s="4" t="inlineStr">
         <is>
-          <t>金貨獲得+%d</t>
+          <t>金币获得+%d</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>働いたら負け</t>
+          <t>工作就输了</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4238,14 +4238,14 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
+          <t>派遣任务</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
           <t>派遣任務</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>派遣任務</t>
-        </is>
-      </c>
       <c r="O29" t="inlineStr">
         <is>
           <t>Dispatch task</t>
@@ -4263,7 +4263,7 @@
       </c>
       <c r="R29" s="4" t="inlineStr">
         <is>
-          <t>無料更新回数+%d</t>
+          <t>免费更新次数+%d</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>タンパク質Ⅱ</t>
+          <t>蛋白质Ⅱ</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>スタミナ回復(昼食)</t>
+          <t>体力恢复（午餐）</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4375,7 +4375,7 @@
       </c>
       <c r="R30" s="4" t="inlineStr">
         <is>
-          <t>経験値獲得+%d</t>
+          <t>获得经验值+%d</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -4407,7 +4407,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>金運上昇Ⅱ</t>
+          <t>财运上升Ⅱ</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>金貨ダンジョン</t>
+          <t>金币地牢</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="R31" s="4" t="inlineStr">
         <is>
-          <t>金貨獲得+%d</t>
+          <t>金币获得+%d</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>功労者Ⅱ</t>
+          <t>功臣Ⅱ</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4574,7 +4574,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>ギルド寄付</t>
+          <t>公会捐赠</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -4599,7 +4599,7 @@
       </c>
       <c r="R32" s="4" t="inlineStr">
         <is>
-          <t>ギルドコイン獲得+%d</t>
+          <t>公会币获得+%d</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>ストーリーモード</t>
+          <t>故事模式</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="R33" s="4" t="inlineStr">
         <is>
-          <t>金貨獲得+%d</t>
+          <t>金币获得+%d</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>スタミナ上限</t>
+          <t>体力上限</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -4855,7 +4855,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>冒険精鋭</t>
+          <t>冒险精英</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4910,14 +4910,14 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
+          <t>日常任务</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
           <t>日常任務</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>日常任務</t>
-        </is>
-      </c>
       <c r="O35" t="inlineStr">
         <is>
           <t>Daily Mission</t>
@@ -4935,7 +4935,7 @@
       </c>
       <c r="R35" s="4" t="inlineStr">
         <is>
-          <t>経験値獲得+%d</t>
+          <t>获得经验值+%d</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>腕相撲Ⅱ</t>
+          <t>摔跤Ⅱ</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="M36" s="4" t="inlineStr">
         <is>
-          <t>経験値ダンジョン</t>
+          <t>经验值地牢</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -5047,7 +5047,7 @@
       </c>
       <c r="R36" s="4" t="inlineStr">
         <is>
-          <t>経験値獲得+%d</t>
+          <t>获得经验值+%d</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -5079,7 +5079,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>交渉術Ⅲ</t>
+          <t>谈判技巧Ⅲ</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5134,7 +5134,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>経験値アイテム購入</t>
+          <t>购买经验值道具</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -5159,7 +5159,7 @@
       </c>
       <c r="R37" s="4" t="inlineStr">
         <is>
-          <t>価格割引+%d</t>
+          <t>价格优惠+%d</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>カフェインⅡ</t>
+          <t>咖啡因Ⅱ</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>スタミナ回復(朝食)</t>
+          <t>恢复体力（早餐）</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -5271,7 +5271,7 @@
       </c>
       <c r="R38" s="4" t="inlineStr">
         <is>
-          <t>スタミナ回復量+%d</t>
+          <t>体力回复量+%d</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>才能開花Ⅱ</t>
+          <t>才华绽放Ⅱ</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5358,7 +5358,7 @@
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>潜能ダンジョン</t>
+          <t>潜能地牢</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="R39" s="4" t="inlineStr">
         <is>
-          <t>産出増加+%d</t>
+          <t>产量增加+%d</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>資産運用家Ⅴ</t>
+          <t>资产管理Ⅴ</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>人生の如くⅢ</t>
+          <t>像人生一样Ⅲ</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5578,7 +5578,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>ハードモード</t>
+          <t>硬模式</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="R41" s="4" t="inlineStr">
         <is>
-          <t>金貨獲得+%d</t>
+          <t>金币获得+%d</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -5635,7 +5635,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>夜のグルメⅡ</t>
+          <t>夜间美食Ⅱ</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -5690,7 +5690,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>スタミナ回復(夜食)</t>
+          <t>恢复体力（夜宵）</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -5715,7 +5715,7 @@
       </c>
       <c r="R42" s="4" t="inlineStr">
         <is>
-          <t>スタミナ回復量+%d</t>
+          <t>体力回复量+%d</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -5747,7 +5747,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>冒険の長老</t>
+          <t>冒险长老</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -5802,14 +5802,14 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
+          <t>日常任务</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
           <t>日常任務</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>日常任務</t>
-        </is>
-      </c>
       <c r="O43" t="inlineStr">
         <is>
           <t>Daily Mission</t>
@@ -5827,7 +5827,7 @@
       </c>
       <c r="R43" s="4" t="inlineStr">
         <is>
-          <t>経験値獲得+%d</t>
+          <t>获得经验值+%d</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>功労者Ⅲ</t>
+          <t>功臣Ⅲ</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -5914,7 +5914,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>ギルド寄付</t>
+          <t>公会捐赠</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -5939,7 +5939,7 @@
       </c>
       <c r="R44" s="4" t="inlineStr">
         <is>
-          <t>ギルドコイン獲得+%d</t>
+          <t>公会币获得+%d</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>紳士の矜持Ⅱ</t>
+          <t>绅士的矜持Ⅱ</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="M45" s="4" t="inlineStr">
         <is>
-          <t>ギフトダンジョン</t>
+          <t>礼品地牢</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="R45" s="4" t="inlineStr">
         <is>
-          <t>産出増加+%d</t>
+          <t>产量增加+%d</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
